--- a/Analysis/Phase2RawAnalysis_Web_Classified.xlsx
+++ b/Analysis/Phase2RawAnalysis_Web_Classified.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/VulnEnvLLM/Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B93076B-ED89-F344-853C-5C1B60692244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD254D7-45A6-214C-8C3F-C74A99EF044F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-2340" windowWidth="19200" windowHeight="20020" activeTab="1" xr2:uid="{FCDB248B-1311-9B4F-B2DC-BA450E98C2F8}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17800" activeTab="2" xr2:uid="{FCDB248B-1311-9B4F-B2DC-BA450E98C2F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Phase2RawAnalysis_Web_Classifie" sheetId="1" r:id="rId1"/>
     <sheet name="RawAnalysis" sheetId="2" r:id="rId2"/>
+    <sheet name="CVEs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Phase2RawAnalysis_Web_Classifie!$A$1:$J$43</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="191">
   <si>
     <t>CVE-2017-12617</t>
   </si>
@@ -2879,4 +2880,67 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4924E43-8F28-2844-B65D-4A5417DFEEF7}">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Analysis/Phase2RawAnalysis_Web_Classified.xlsx
+++ b/Analysis/Phase2RawAnalysis_Web_Classified.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD254D7-45A6-214C-8C3F-C74A99EF044F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E557246-252D-024D-85A2-76F86C000507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17800" activeTab="2" xr2:uid="{FCDB248B-1311-9B4F-B2DC-BA450E98C2F8}"/>
+    <workbookView xWindow="34560" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{FCDB248B-1311-9B4F-B2DC-BA450E98C2F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Phase2RawAnalysis_Web_Classifie" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="CVEs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Phase2RawAnalysis_Web_Classifie!$A$1:$J$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Phase2RawAnalysis_Web_Classifie!$A$1:$J$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">RawAnalysis!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="190">
   <si>
     <t>CVE-2017-12617</t>
   </si>
@@ -402,10 +402,6 @@
   </si>
   <si>
     <t>Changes to work</t>
-  </si>
-  <si>
-    <t>1. No showcase with example
-2. invalid struts version</t>
   </si>
   <si>
     <t>1. Fix archived Debian repository resolution for EOL buster base image` and switched APT sources to `archive.debian.org` with `Acquire::Check-Valid-Until "false"`.
@@ -1059,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6425BED-5B03-6C48-BFEE-D40FE3A87220}">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.140625" customWidth="1"/>
@@ -1077,28 +1073,28 @@
         <v>112</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="E1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="G1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1124,7 +1120,7 @@
         <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I2" t="s">
         <v>7</v>
@@ -1156,7 +1152,7 @@
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
@@ -1188,7 +1184,7 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -1211,16 +1207,16 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
+        <v>187</v>
+      </c>
+      <c r="F5" t="s">
         <v>188</v>
-      </c>
-      <c r="F5" t="s">
-        <v>189</v>
       </c>
       <c r="G5" t="s">
         <v>6</v>
       </c>
       <c r="H5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I5" t="s">
         <v>25</v>
@@ -1252,7 +1248,7 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I6" t="s">
         <v>28</v>
@@ -1284,7 +1280,7 @@
         <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I7" t="s">
         <v>28</v>
@@ -1316,7 +1312,7 @@
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I8" t="s">
         <v>33</v>
@@ -1348,7 +1344,7 @@
         <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I9" t="s">
         <v>39</v>
@@ -1380,7 +1376,7 @@
         <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I10" t="s">
         <v>44</v>
@@ -1403,16 +1399,16 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
+        <v>187</v>
+      </c>
+      <c r="F11" t="s">
         <v>188</v>
-      </c>
-      <c r="F11" t="s">
-        <v>189</v>
       </c>
       <c r="G11" t="s">
         <v>6</v>
       </c>
       <c r="H11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I11" t="s">
         <v>25</v>
@@ -1444,7 +1440,7 @@
         <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I12" t="s">
         <v>28</v>
@@ -1476,7 +1472,7 @@
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I13" t="s">
         <v>52</v>
@@ -1508,7 +1504,7 @@
         <v>6</v>
       </c>
       <c r="H14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I14" t="s">
         <v>57</v>
@@ -1540,7 +1536,7 @@
         <v>6</v>
       </c>
       <c r="H15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I15" t="s">
         <v>60</v>
@@ -1572,7 +1568,7 @@
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1604,7 +1600,7 @@
         <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I17" t="s">
         <v>68</v>
@@ -1636,7 +1632,7 @@
         <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I18" t="s">
         <v>71</v>
@@ -1659,16 +1655,16 @@
         <v>3</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="G19" t="s">
         <v>6</v>
       </c>
       <c r="H19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I19" t="s">
         <v>74</v>
@@ -1700,7 +1696,7 @@
         <v>6</v>
       </c>
       <c r="H20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I20" t="s">
         <v>78</v>
@@ -1726,13 +1722,13 @@
         <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G21" t="s">
         <v>6</v>
       </c>
       <c r="H21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I21" t="s">
         <v>81</v>
@@ -1758,13 +1754,13 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G22" t="s">
         <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I22" t="s">
         <v>84</v>
@@ -1796,7 +1792,7 @@
         <v>6</v>
       </c>
       <c r="H23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I23" t="s">
         <v>78</v>
@@ -1819,16 +1815,16 @@
         <v>3</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="G24" t="s">
         <v>6</v>
       </c>
       <c r="H24" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I24" t="s">
         <v>89</v>
@@ -1854,13 +1850,13 @@
         <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G25" t="s">
         <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I25" t="s">
         <v>92</v>
@@ -1892,7 +1888,7 @@
         <v>67</v>
       </c>
       <c r="H26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I26" t="s">
         <v>96</v>
@@ -1924,7 +1920,7 @@
         <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I27" t="s">
         <v>99</v>
@@ -1956,7 +1952,7 @@
         <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I28" t="s">
         <v>103</v>
@@ -1979,16 +1975,16 @@
         <v>3</v>
       </c>
       <c r="E29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="G29" t="s">
         <v>6</v>
       </c>
       <c r="H29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I29" t="s">
         <v>106</v>
@@ -2014,13 +2010,13 @@
         <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G30" t="s">
         <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I30" t="s">
         <v>109</v>
@@ -2031,141 +2027,141 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E31" t="s">
-        <v>159</v>
+        <v>37</v>
       </c>
       <c r="F31" t="s">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="G31" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I31" t="s">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="J31" t="s">
-        <v>162</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" t="s">
-        <v>50</v>
-      </c>
-      <c r="F32" t="s">
-        <v>51</v>
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="G32" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I32" t="s">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="J32" t="s">
-        <v>164</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>156</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s">
         <v>3</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>188</v>
+        <v>24</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G33" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I33" t="s">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="J33" t="s">
-        <v>165</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B34" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
       </c>
       <c r="E34" t="s">
+        <v>158</v>
+      </c>
+      <c r="F34" t="s">
         <v>159</v>
-      </c>
-      <c r="F34" t="s">
-        <v>160</v>
       </c>
       <c r="G34" t="s">
         <v>67</v>
       </c>
       <c r="H34" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I34" t="s">
+        <v>160</v>
+      </c>
+      <c r="J34" t="s">
         <v>161</v>
-      </c>
-      <c r="J34" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B35" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -2180,97 +2176,97 @@
         <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I35" t="s">
+        <v>162</v>
+      </c>
+      <c r="J35" t="s">
         <v>163</v>
-      </c>
-      <c r="J35" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B36" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D36" t="s">
         <v>3</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="G36" t="s">
         <v>6</v>
       </c>
       <c r="H36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
         <v>153</v>
-      </c>
-      <c r="B37" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37" t="s">
-        <v>167</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
       </c>
       <c r="E37" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="F37" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G37" t="s">
         <v>67</v>
       </c>
       <c r="H37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I37" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="J37" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D38" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="E38" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F38" t="s">
-        <v>181</v>
+        <v>51</v>
       </c>
       <c r="G38" t="s">
         <v>20</v>
@@ -2279,153 +2275,249 @@
         <v>142</v>
       </c>
       <c r="I38" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="J38" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="D39" t="s">
-        <v>174</v>
-      </c>
-      <c r="E39" t="s">
-        <v>37</v>
-      </c>
-      <c r="F39" t="s">
-        <v>181</v>
+        <v>3</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="G39" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I39" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="J39" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B40" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
       </c>
       <c r="E40" t="s">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="F40" t="s">
-        <v>51</v>
+        <v>178</v>
       </c>
       <c r="G40" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="H40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I40" t="s">
+        <v>179</v>
+      </c>
+      <c r="J40" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>173</v>
       </c>
       <c r="E41" t="s">
-        <v>178</v>
+        <v>37</v>
       </c>
       <c r="F41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G41" t="s">
         <v>20</v>
       </c>
       <c r="H41" t="s">
-        <v>142</v>
+        <v>141</v>
+      </c>
+      <c r="I41" t="s">
+        <v>181</v>
+      </c>
+      <c r="J41" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B42" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E42" t="s">
         <v>37</v>
       </c>
       <c r="F42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G42" t="s">
         <v>20</v>
       </c>
       <c r="H42" t="s">
-        <v>142</v>
+        <v>140</v>
+      </c>
+      <c r="I42" t="s">
+        <v>182</v>
+      </c>
+      <c r="J42" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D43" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F43" t="s">
-        <v>181</v>
+        <v>51</v>
       </c>
       <c r="G43" t="s">
         <v>20</v>
       </c>
       <c r="H43" t="s">
+        <v>142</v>
+      </c>
+      <c r="I43" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>175</v>
+      </c>
+      <c r="D44" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" t="s">
+        <v>177</v>
+      </c>
+      <c r="F44" t="s">
+        <v>178</v>
+      </c>
+      <c r="G44" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44" t="s">
         <v>141</v>
       </c>
     </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>152</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" t="s">
+        <v>37</v>
+      </c>
+      <c r="F45" t="s">
+        <v>180</v>
+      </c>
+      <c r="G45" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>171</v>
+      </c>
+      <c r="D46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E46" t="s">
+        <v>37</v>
+      </c>
+      <c r="F46" t="s">
+        <v>180</v>
+      </c>
+      <c r="G46" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" t="s">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J43" xr:uid="{F6425BED-5B03-6C48-BFEE-D40FE3A87220}"/>
+  <autoFilter ref="A1:J46" xr:uid="{F6425BED-5B03-6C48-BFEE-D40FE3A87220}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -2475,7 +2567,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="140" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2491,11 +2583,9 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" ht="360" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -2518,10 +2608,10 @@
         <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2538,19 +2628,19 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:10" ht="300" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -2567,16 +2657,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:10" ht="260" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -2593,19 +2683,19 @@
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" t="s">
         <v>130</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:10" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>76</v>
       </c>
@@ -2622,13 +2712,13 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>76</v>
       </c>
@@ -2648,10 +2738,10 @@
         <v>86</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="280" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="240" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>87</v>
       </c>
@@ -2668,10 +2758,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="40" x14ac:dyDescent="0.25">
@@ -2694,7 +2784,7 @@
         <v>95</v>
       </c>
       <c r="J10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="80" x14ac:dyDescent="0.25">
@@ -2717,10 +2807,10 @@
         <v>98</v>
       </c>
       <c r="J11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="360" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>101</v>
       </c>
@@ -2740,13 +2830,13 @@
         <v>102</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:10" ht="360" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>101</v>
       </c>
@@ -2754,21 +2844,27 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="200" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
@@ -2786,18 +2882,18 @@
         <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H14" t="s">
         <v>155</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="140" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B15" t="s">
         <v>1</v>
@@ -2815,15 +2911,15 @@
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H15" t="s">
         <v>155</v>
-      </c>
-      <c r="H15" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
@@ -2841,18 +2937,18 @@
         <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H16" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="140" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
@@ -2873,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2932,12 +3028,12 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
